--- a/data/trans_dic/IP1004-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1004-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen diabetes</t>
+          <t>Menores que padecen diabetes (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,96</t>
+          <t>0,33; 3,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,67</t>
+          <t>0,15; 1,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 3,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,49</t>
+          <t>0,18; 1,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,66</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,02</t>
+          <t>0,16; 0,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,85</t>
+          <t>0,1; 0,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,67</t>
+          <t>0,14; 0,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,57</t>
+          <t>0,06; 0,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,33</t>
+          <t>0,0; 0,3</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen diabetes (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3603</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4146</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3849</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4519</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2582</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2582</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>701; 6510</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>621; 6236</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3387</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5119</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3929</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4298</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2312</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3429</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4762</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5301</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3722</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>738; 6111</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4671</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3170</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4343</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3959</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1187; 6886</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>745; 7074</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1918; 8974</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>855; 7863</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4354</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1004-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1004-Habitat-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,07</t>
+          <t>0,29; 2,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,53</t>
+          <t>0,15; 1,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,46</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,27 +1118,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,95</t>
+          <t>0,18; 1,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,95</t>
+          <t>0,1; 0,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,64</t>
+          <t>0,14; 0,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,54</t>
+          <t>0,05; 0,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,3</t>
+          <t>0,0; 0,33</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3603</t>
+          <t>0; 3677</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4146</t>
+          <t>0; 4817</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3849</t>
+          <t>0; 2964</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4519</t>
+          <t>0; 4714</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>701; 6510</t>
+          <t>617; 6096</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>621; 6236</t>
+          <t>619; 5851</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3387</t>
+          <t>0; 3842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5119</t>
+          <t>0; 3712</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3929</t>
+          <t>0; 3388</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4298</t>
+          <t>0; 4658</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3429</t>
+          <t>0; 3099</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4762</t>
+          <t>0; 4696</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5301</t>
+          <t>0; 5300</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3722</t>
+          <t>0; 2986</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>738; 6111</t>
+          <t>0; 6205</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2069,27 +2069,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4343</t>
+          <t>0; 4247</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3959</t>
+          <t>0; 4960</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5276</t>
+          <t>0; 4776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1187; 6886</t>
+          <t>1266; 7731</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>745; 7074</t>
+          <t>749; 6483</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2099,17 +2099,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1918; 8974</t>
+          <t>2003; 8788</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>855; 7863</t>
+          <t>791; 8042</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4354</t>
+          <t>0; 4712</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1004-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1004-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -703,12 +703,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
     </row>
@@ -735,22 +735,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,29; 2,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,44</t>
+          <t>0,17; 1,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,27 +955,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,18; 1,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,42 +1118,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,16; 1,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,1; 0,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,07</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,87</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,63</t>
+          <t>0,12; 0,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,55</t>
+          <t>0,06; 0,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>732</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1360</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3677</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4817</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4903</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5074</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2964</t>
+          <t>0; 3680</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4714</t>
+          <t>0; 5110</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>620; 6269</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>617; 6096</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>619; 5851</t>
+          <t>701; 6821</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>857</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3486</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4554</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3842</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3712</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3388</t>
+          <t>0; 3372</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4658</t>
+          <t>0; 4341</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1800,27 +1800,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,27 +1853,27 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>683</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>790</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1522</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3099</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4696</t>
+          <t>0; 4659</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4567</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5300</t>
+          <t>0; 3980</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2986</t>
+          <t>0; 3433</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6205</t>
+          <t>743; 6202</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1415</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1360</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4247</t>
+          <t>1187; 7372</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4960</t>
+          <t>745; 6347</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4776</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1266; 7731</t>
+          <t>0; 4515</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>749; 6483</t>
+          <t>0; 4559</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5576</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2003; 8788</t>
+          <t>1729; 9392</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>791; 8042</t>
+          <t>853; 8280</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4712</t>
+          <t>0; 4825</t>
         </is>
       </c>
     </row>
